--- a/python/output/EPS.xlsx
+++ b/python/output/EPS.xlsx
@@ -447,1583 +447,1583 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>8572</v>
+        <v>3883</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.55555558</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>8573</v>
+        <v>3884</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.58333331</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>8574</v>
+        <v>3885</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.6111111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>15291</v>
+        <v>3911</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0.6111111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>15341</v>
+        <v>3912</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0.6388889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>15362</v>
+        <v>3913</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0.72222221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>15363</v>
+        <v>3914</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>0.72222221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>15433</v>
+        <v>3915</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0.72222221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>15435</v>
+        <v>3916</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>15436</v>
+        <v>3942</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>15591</v>
+        <v>3943</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2014</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0.77777779</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>19937</v>
+        <v>3944</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6944444</v>
+        <v>0.77777779</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>19938</v>
+        <v>3945</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6944444</v>
+        <v>0.77777779</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>19939</v>
+        <v>3946</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6944444</v>
+        <v>0.77777779</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>19940</v>
+        <v>3947</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D16" t="n">
-        <v>2.75</v>
+        <v>0.83333331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>19941</v>
+        <v>3973</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8611112</v>
+        <v>0.83333331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>19942</v>
+        <v>3974</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8611112</v>
+        <v>0.83333331</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>19943</v>
+        <v>3975</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9166667</v>
+        <v>0.83333331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>19968</v>
+        <v>3976</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1111112</v>
+        <v>0.83333331</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19969</v>
+        <v>3977</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D21" t="n">
-        <v>2.9444444</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>19970</v>
+        <v>3978</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D22" t="n">
-        <v>2.9444444</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>19971</v>
+        <v>4004</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D23" t="n">
-        <v>2.9444444</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>19972</v>
+        <v>4005</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D24" t="n">
-        <v>3.0833333</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>19973</v>
+        <v>4006</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1388888</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>19974</v>
+        <v>4007</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D26" t="n">
-        <v>3.3055556</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>19999</v>
+        <v>4008</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D27" t="n">
-        <v>2.9444444</v>
+        <v>0.8611111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>20000</v>
+        <v>4032</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D28" t="n">
-        <v>2.8333333</v>
+        <v>0.8888889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>20001</v>
+        <v>4033</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D29" t="n">
-        <v>2.8888888</v>
+        <v>0.8888889</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>20002</v>
+        <v>4034</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D30" t="n">
-        <v>2.9444444</v>
+        <v>0.8888889</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>20003</v>
+        <v>4035</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2019</v>
       </c>
       <c r="D31" t="n">
-        <v>3.2222223</v>
+        <v>0.8888889</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>20004</v>
+        <v>4036</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2020</v>
       </c>
       <c r="D32" t="n">
-        <v>3.4444444</v>
+        <v>0.8888889</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>20029</v>
+        <v>4037</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="D33" t="n">
-        <v>3.1944444</v>
+        <v>0.91666669</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>20030</v>
+        <v>4110</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D34" t="n">
-        <v>2.5277777</v>
+        <v>0.91666669</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>20031</v>
+        <v>4111</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D35" t="n">
-        <v>2.3611112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>20032</v>
+        <v>4112</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D36" t="n">
-        <v>2.5833333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>20033</v>
+        <v>4113</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D37" t="n">
-        <v>2.6944444</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>20034</v>
+        <v>4114</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D38" t="n">
-        <v>2.6388888</v>
+        <v>1.0833334</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>20035</v>
+        <v>4115</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D39" t="n">
-        <v>3.0277777</v>
+        <v>1.0833334</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>20050</v>
+        <v>4296</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D40" t="n">
-        <v>1.9166666</v>
+        <v>1.0833334</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>20051</v>
+        <v>4297</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D41" t="n">
-        <v>1.9722222</v>
+        <v>1.0833334</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>20052</v>
+        <v>8729</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2016</v>
       </c>
       <c r="D42" t="n">
-        <v>1.9722222</v>
+        <v>1.1666666</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>20053</v>
+        <v>9920</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2017</v>
       </c>
       <c r="D43" t="n">
-        <v>2.0277777</v>
+        <v>1.1666666</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>20054</v>
+        <v>9921</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2018</v>
       </c>
       <c r="D44" t="n">
-        <v>2.0277777</v>
+        <v>1.1666666</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>20055</v>
+        <v>9922</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2019</v>
       </c>
       <c r="D45" t="n">
-        <v>2.0277777</v>
+        <v>1.1666666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>20056</v>
+        <v>9927</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2020</v>
       </c>
       <c r="D46" t="n">
-        <v>2.0277777</v>
+        <v>1.1666666</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>20080</v>
+        <v>9928</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D47" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>20081</v>
+        <v>9929</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D48" t="n">
-        <v>2.5555556</v>
+        <v>1.3055556</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>20082</v>
+        <v>9934</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D49" t="n">
-        <v>2.7222223</v>
+        <v>1.4722222</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>20083</v>
+        <v>9935</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D50" t="n">
-        <v>2.7222223</v>
+        <v>1.4722222</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>20084</v>
+        <v>9936</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D51" t="n">
-        <v>2.8888888</v>
+        <v>1.4722222</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>20085</v>
+        <v>9937</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D52" t="n">
-        <v>3.1111112</v>
+        <v>1.4722222</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>20086</v>
+        <v>9938</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D53" t="n">
-        <v>2.9444444</v>
+        <v>1.4722222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>20109</v>
+        <v>9939</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D54" t="n">
-        <v>4.1111112</v>
+        <v>1.5555556</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>20110</v>
+        <v>9940</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D55" t="n">
-        <v>4.0277777</v>
+        <v>1.5833334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>20111</v>
+        <v>9945</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D56" t="n">
-        <v>3.9444444</v>
+        <v>1.5833334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>20112</v>
+        <v>9946</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D57" t="n">
-        <v>4.0277777</v>
+        <v>1.6388888</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>20113</v>
+        <v>9947</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D58" t="n">
-        <v>3.7777777</v>
+        <v>1.8611112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>20114</v>
+        <v>9952</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D59" t="n">
-        <v>3.6666667</v>
+        <v>1.9166666</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>20115</v>
+        <v>9953</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D60" t="n">
-        <v>3.7222223</v>
+        <v>1.9722222</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>20138</v>
+        <v>9954</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D61" t="n">
-        <v>3.7222223</v>
+        <v>1.9722222</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>20139</v>
+        <v>9958</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D62" t="n">
-        <v>3.7222223</v>
+        <v>1.9722222</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>20140</v>
+        <v>9962</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D63" t="n">
-        <v>3.7222223</v>
+        <v>2.0277777</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>20141</v>
+        <v>9963</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D64" t="n">
-        <v>3.7777777</v>
+        <v>2.0277777</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>20142</v>
+        <v>9964</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D65" t="n">
-        <v>3.3333333</v>
+        <v>2.0277777</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>20143</v>
+        <v>9969</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D66" t="n">
-        <v>3.1666667</v>
+        <v>2.0277777</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>20144</v>
+        <v>9970</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D67" t="n">
-        <v>3.2777777</v>
+        <v>2.1111112</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>20168</v>
+        <v>9971</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D68" t="n">
-        <v>3.6944444</v>
+        <v>2.1666667</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>20169</v>
+        <v>9976</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D69" t="n">
-        <v>3.8611112</v>
+        <v>2.2777777</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>20170</v>
+        <v>9977</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D70" t="n">
-        <v>3.8333333</v>
+        <v>2.2777777</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>20171</v>
+        <v>9978</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D71" t="n">
-        <v>3.8333333</v>
+        <v>2.3611112</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>20172</v>
+        <v>9983</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D72" t="n">
-        <v>3.9166667</v>
+        <v>2.3888888</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>20173</v>
+        <v>9984</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D73" t="n">
-        <v>3.8055556</v>
+        <v>2.3888888</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>20174</v>
+        <v>9985</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="D74" t="n">
-        <v>4.1111112</v>
+        <v>2.3888888</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>20198</v>
+        <v>9990</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D75" t="n">
-        <v>4.2222223</v>
+        <v>2.3888888</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>20199</v>
+        <v>9991</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D76" t="n">
-        <v>4.0277777</v>
+        <v>2.3888888</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>20200</v>
+        <v>9992</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D77" t="n">
-        <v>3.9166667</v>
+        <v>2.4166667</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>20201</v>
+        <v>9997</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2017</v>
       </c>
       <c r="D78" t="n">
-        <v>4.1666665</v>
+        <v>2.4166667</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>20202</v>
+        <v>9998</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D79" t="n">
-        <v>4.5555553</v>
+        <v>2.4444444</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>20203</v>
+        <v>9999</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D80" t="n">
-        <v>4.7222223</v>
+        <v>2.4444444</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>20204</v>
+        <v>10004</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D81" t="n">
-        <v>4.8888888</v>
+        <v>2.4444444</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>20229</v>
+        <v>12547</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D82" t="n">
-        <v>3.1111112</v>
+        <v>2.4444444</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>20230</v>
+        <v>12555</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>2015</v>
       </c>
       <c r="D83" t="n">
-        <v>3.0277777</v>
+        <v>2.4722221</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>20231</v>
+        <v>13140</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D84" t="n">
-        <v>3.0833333</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>20232</v>
+        <v>13141</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D85" t="n">
-        <v>3.0277777</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>20233</v>
+        <v>13142</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>2018</v>
       </c>
       <c r="D86" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>20234</v>
+        <v>13143</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D87" t="n">
-        <v>3.3055556</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>20235</v>
+        <v>13157</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>2020</v>
       </c>
       <c r="D88" t="n">
-        <v>3.4722223</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>20260</v>
+        <v>13158</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>2014</v>
       </c>
       <c r="D89" t="n">
-        <v>2.8888888</v>
+        <v>2.5277777</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>20261</v>
+        <v>13159</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>2015</v>
       </c>
       <c r="D90" t="n">
-        <v>3.0555556</v>
+        <v>2.5277777</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>20262</v>
+        <v>13160</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>2016</v>
       </c>
       <c r="D91" t="n">
-        <v>2.8888888</v>
+        <v>2.5277777</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>20263</v>
+        <v>13161</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>2017</v>
       </c>
       <c r="D92" t="n">
-        <v>2.8611112</v>
+        <v>2.5277777</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>20264</v>
+        <v>13162</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D93" t="n">
-        <v>2.8611112</v>
+        <v>2.5555556</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>20265</v>
+        <v>13163</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D94" t="n">
-        <v>2.8333333</v>
+        <v>2.5555556</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>20266</v>
+        <v>13167</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D95" t="n">
-        <v>2.8888888</v>
+        <v>2.5555556</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>20291</v>
+        <v>13168</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D96" t="n">
-        <v>2.8888888</v>
+        <v>2.5833333</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>20292</v>
+        <v>13169</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>2015</v>
       </c>
       <c r="D97" t="n">
-        <v>2.9722223</v>
+        <v>2.6111112</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>20293</v>
+        <v>13170</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D98" t="n">
-        <v>2.6944444</v>
+        <v>2.6388888</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>20294</v>
+        <v>13171</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D99" t="n">
-        <v>3.1111112</v>
+        <v>2.6666667</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>20295</v>
+        <v>13172</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D100" t="n">
         <v>2.6944444</v>
@@ -2031,1191 +2031,1191 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>20296</v>
+        <v>13173</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D101" t="n">
-        <v>2.75</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>20297</v>
+        <v>13174</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="D102" t="n">
-        <v>2.8055556</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>20304</v>
+        <v>13180</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D103" t="n">
-        <v>0.72222221</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>20305</v>
+        <v>13187</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D104" t="n">
-        <v>0.72222221</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>20306</v>
+        <v>13198</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D105" t="n">
-        <v>0.72222221</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>20307</v>
+        <v>13199</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D106" t="n">
-        <v>0.77777779</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>20332</v>
+        <v>13200</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="D107" t="n">
-        <v>2.8611112</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>20333</v>
+        <v>13201</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D108" t="n">
-        <v>2.8611112</v>
+        <v>2.6944444</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>20334</v>
+        <v>13202</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>2016</v>
       </c>
       <c r="D109" t="n">
-        <v>2.5</v>
+        <v>2.7222223</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>20335</v>
+        <v>13203</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>2017</v>
       </c>
       <c r="D110" t="n">
-        <v>2.4444444</v>
+        <v>2.7222223</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>20336</v>
+        <v>13204</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>2018</v>
       </c>
       <c r="D111" t="n">
-        <v>2.5</v>
+        <v>2.7222223</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>20337</v>
+        <v>13205</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D112" t="n">
-        <v>2.5555556</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>20359</v>
+        <v>13206</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D113" t="n">
-        <v>0.55555558</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>20360</v>
+        <v>13207</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D114" t="n">
-        <v>0.6111111</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>20361</v>
+        <v>13208</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>2016</v>
       </c>
       <c r="D115" t="n">
-        <v>0.6111111</v>
+        <v>2.7777777</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>20362</v>
+        <v>13209</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>2017</v>
       </c>
       <c r="D116" t="n">
-        <v>0.77777779</v>
+        <v>2.7777777</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>20363</v>
+        <v>13210</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D117" t="n">
-        <v>0.8611111</v>
+        <v>2.7777777</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>20364</v>
+        <v>13211</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D118" t="n">
-        <v>0.8611111</v>
+        <v>2.8055556</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>20365</v>
+        <v>13212</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D119" t="n">
-        <v>1.0833334</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>20390</v>
+        <v>13213</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>2015</v>
       </c>
       <c r="D120" t="n">
-        <v>4.0555553</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>20391</v>
+        <v>13214</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D121" t="n">
-        <v>4.0555553</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>20392</v>
+        <v>13699</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D122" t="n">
-        <v>4.0555553</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>20393</v>
+        <v>14187</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D123" t="n">
-        <v>3.7777777</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>20394</v>
+        <v>14199</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>2019</v>
       </c>
       <c r="D124" t="n">
-        <v>3.75</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>20395</v>
+        <v>15094</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>2020</v>
       </c>
       <c r="D125" t="n">
-        <v>3.7222223</v>
+        <v>2.8333333</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>20419</v>
+        <v>15095</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>2014</v>
       </c>
       <c r="D126" t="n">
-        <v>3.8333333</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>20420</v>
+        <v>15101</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>2015</v>
       </c>
       <c r="D127" t="n">
-        <v>3.7222221</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>20421</v>
+        <v>15110</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D128" t="n">
-        <v>3.9444444</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>20422</v>
+        <v>15118</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D129" t="n">
-        <v>3.8888888</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>20423</v>
+        <v>15119</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>2018</v>
       </c>
       <c r="D130" t="n">
-        <v>3.6111112</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>20424</v>
+        <v>15120</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D131" t="n">
-        <v>3.7777777</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>20425</v>
+        <v>15121</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D132" t="n">
-        <v>3.7777777</v>
+        <v>2.8611112</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>20448</v>
+        <v>15126</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>2014</v>
       </c>
       <c r="D133" t="n">
-        <v>2.8333333</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>20449</v>
+        <v>15127</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D134" t="n">
-        <v>2.9444444</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>20450</v>
+        <v>15129</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D135" t="n">
-        <v>3.1111112</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>20451</v>
+        <v>15130</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D136" t="n">
-        <v>3.1666667</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>20452</v>
+        <v>15132</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D137" t="n">
-        <v>3.1666667</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>20477</v>
+        <v>15133</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D138" t="n">
-        <v>3.8888888</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>20478</v>
+        <v>15135</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D139" t="n">
-        <v>3.8888888</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>20479</v>
+        <v>15136</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D140" t="n">
-        <v>3.9444444</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>20480</v>
+        <v>15138</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D141" t="n">
-        <v>3.8888888</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>20481</v>
+        <v>15139</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D142" t="n">
-        <v>3.9444444</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>20482</v>
+        <v>15141</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D143" t="n">
-        <v>4.1666665</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>20483</v>
+        <v>15142</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>2020</v>
       </c>
       <c r="D144" t="n">
-        <v>4.2222223</v>
+        <v>2.8888888</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>20506</v>
+        <v>15144</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="D145" t="n">
-        <v>1.4722222</v>
+        <v>2.9166667</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>20507</v>
+        <v>15145</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D146" t="n">
-        <v>1.4722222</v>
+        <v>2.9166667</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>20508</v>
+        <v>15147</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D147" t="n">
-        <v>1.4722222</v>
+        <v>2.9166667</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>20509</v>
+        <v>15148</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D148" t="n">
-        <v>1.4722222</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>20510</v>
+        <v>15150</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D149" t="n">
-        <v>1.4722222</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>20511</v>
+        <v>15151</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D150" t="n">
-        <v>1.5833334</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>20512</v>
+        <v>15153</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D151" t="n">
-        <v>1.5833334</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>20537</v>
+        <v>15154</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D152" t="n">
-        <v>3.1111112</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>20538</v>
+        <v>15156</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D153" t="n">
-        <v>3.1944444</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>20539</v>
+        <v>15157</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>2016</v>
       </c>
       <c r="D154" t="n">
-        <v>3.3333333</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>20540</v>
+        <v>15159</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>2017</v>
       </c>
       <c r="D155" t="n">
-        <v>3.1111112</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>20541</v>
+        <v>15160</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D156" t="n">
-        <v>3.5</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>20542</v>
+        <v>15162</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>2019</v>
       </c>
       <c r="D157" t="n">
-        <v>3.4722223</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>20543</v>
+        <v>15163</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>2020</v>
       </c>
       <c r="D158" t="n">
-        <v>3.4722223</v>
+        <v>2.9444444</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>20568</v>
+        <v>15164</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D159" t="n">
-        <v>0.77777779</v>
+        <v>2.9722221</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>20569</v>
+        <v>15165</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D160" t="n">
-        <v>0.77777779</v>
+        <v>2.9722221</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>20570</v>
+        <v>15166</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D161" t="n">
-        <v>0.83333331</v>
+        <v>2.9722223</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>20571</v>
+        <v>15433</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D162" t="n">
-        <v>0.83333331</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>20572</v>
+        <v>15591</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D163" t="n">
-        <v>0.83333331</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>20573</v>
+        <v>15833</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D164" t="n">
-        <v>0.83333331</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>20574</v>
+        <v>17773</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D165" t="n">
-        <v>0.83333331</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>20599</v>
+        <v>17774</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="D166" t="n">
-        <v>3.7222223</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>20600</v>
+        <v>17775</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D167" t="n">
-        <v>3.7222223</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>20601</v>
+        <v>17777</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D168" t="n">
-        <v>3.7222223</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>20602</v>
+        <v>17787</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D169" t="n">
-        <v>3.7222223</v>
+        <v>3.0277777</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>20603</v>
+        <v>17799</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D170" t="n">
-        <v>3.8333333</v>
+        <v>3.0277777</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>20604</v>
+        <v>17800</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D171" t="n">
-        <v>3.8888888</v>
+        <v>3.0277777</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>20605</v>
+        <v>17801</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C172" t="n">
         <v>2020</v>
       </c>
       <c r="D172" t="n">
-        <v>3.9444444</v>
+        <v>3.0277777</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>20629</v>
+        <v>17809</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D173" t="n">
-        <v>2.9444444</v>
+        <v>3.0555556</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>20630</v>
+        <v>17818</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D174" t="n">
-        <v>2.9444444</v>
+        <v>3.0555556</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>20631</v>
+        <v>17819</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3223,303 +3223,303 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D175" t="n">
-        <v>2.8333333</v>
+        <v>3.0555556</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>20632</v>
+        <v>17820</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D176" t="n">
-        <v>2.8888888</v>
+        <v>3.0833333</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>20633</v>
+        <v>17821</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>2018</v>
       </c>
       <c r="D177" t="n">
-        <v>3.0555556</v>
+        <v>3.0833333</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>20634</v>
+        <v>17834</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D178" t="n">
-        <v>3.4166667</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>20635</v>
+        <v>17835</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D179" t="n">
-        <v>3.4722223</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>20660</v>
+        <v>17836</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>2014</v>
       </c>
       <c r="D180" t="n">
-        <v>2.1111112</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>20661</v>
+        <v>17837</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D181" t="n">
-        <v>2.1666667</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>20662</v>
+        <v>17850</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D182" t="n">
-        <v>2.3888888</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>20663</v>
+        <v>17851</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D183" t="n">
-        <v>2.3888888</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>20664</v>
+        <v>17852</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D184" t="n">
-        <v>2.3888888</v>
+        <v>3.1111112</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>20665</v>
+        <v>17853</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C185" t="n">
         <v>2019</v>
       </c>
       <c r="D185" t="n">
-        <v>2.6666667</v>
+        <v>3.1388888</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>20666</v>
+        <v>17854</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>2020</v>
       </c>
       <c r="D186" t="n">
-        <v>2.7777777</v>
+        <v>3.1388888</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>20691</v>
+        <v>17855</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D187" t="n">
-        <v>2.8333333</v>
+        <v>3.1666667</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>20692</v>
+        <v>17863</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D188" t="n">
-        <v>3.0555556</v>
+        <v>3.1666667</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>20693</v>
+        <v>17864</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D189" t="n">
-        <v>2.4166667</v>
+        <v>3.1666667</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>20694</v>
+        <v>17865</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D190" t="n">
-        <v>2.5555556</v>
+        <v>3.1666667</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>20695</v>
+        <v>17875</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D191" t="n">
-        <v>2.4444444</v>
+        <v>3.1944444</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>20696</v>
+        <v>17876</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D192" t="n">
-        <v>2.5</v>
+        <v>3.1944444</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>20715</v>
+        <v>17877</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D193" t="n">
-        <v>2.8888888</v>
+        <v>3.2222223</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>20716</v>
+        <v>17878</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -3527,607 +3527,607 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D194" t="n">
-        <v>2.8888888</v>
+        <v>3.2222223</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>20717</v>
+        <v>17879</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D195" t="n">
-        <v>2.9444444</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>20718</v>
+        <v>17885</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D196" t="n">
-        <v>3.1666667</v>
+        <v>3.2777777</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>20719</v>
+        <v>17890</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D197" t="n">
-        <v>3.2222223</v>
+        <v>3.3055556</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>20744</v>
+        <v>17891</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D198" t="n">
-        <v>2.3888888</v>
+        <v>3.3055556</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>20745</v>
+        <v>17892</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D199" t="n">
-        <v>2.3888888</v>
+        <v>3.3333333</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>20746</v>
+        <v>17908</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D200" t="n">
-        <v>2.2777777</v>
+        <v>3.3333333</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>20747</v>
+        <v>17935</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D201" t="n">
-        <v>2.2777777</v>
+        <v>3.3611112</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>20748</v>
+        <v>17936</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D202" t="n">
-        <v>2.4444444</v>
+        <v>3.4166667</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>20749</v>
+        <v>17937</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D203" t="n">
-        <v>2.4444444</v>
+        <v>3.4444444</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>20750</v>
+        <v>18890</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D204" t="n">
-        <v>2.5</v>
+        <v>3.4722223</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>20775</v>
+        <v>19937</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D205" t="n">
-        <v>3.5555556</v>
+        <v>3.4722223</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>20776</v>
+        <v>19968</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D206" t="n">
-        <v>3.6111112</v>
+        <v>3.4722223</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>20777</v>
+        <v>19999</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D207" t="n">
-        <v>3.6666667</v>
+        <v>3.4722223</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>20778</v>
+        <v>20029</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D208" t="n">
-        <v>3.6111112</v>
+        <v>3.4722223</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>20779</v>
+        <v>20050</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>2018</v>
       </c>
       <c r="D209" t="n">
-        <v>3.6666667</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>20780</v>
+        <v>20051</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D210" t="n">
-        <v>3.6111112</v>
+        <v>3.5277777</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>20781</v>
+        <v>20080</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D211" t="n">
-        <v>3.8333333</v>
+        <v>3.5277777</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>20806</v>
+        <v>20109</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C212" t="n">
         <v>2014</v>
       </c>
       <c r="D212" t="n">
-        <v>4.0555553</v>
+        <v>3.5555556</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>20807</v>
+        <v>20138</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C213" t="n">
         <v>2015</v>
       </c>
       <c r="D213" t="n">
-        <v>4.0277777</v>
+        <v>3.6111112</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>20808</v>
+        <v>20168</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D214" t="n">
-        <v>4.1388888</v>
+        <v>3.6111112</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>20809</v>
+        <v>20198</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D215" t="n">
-        <v>4.1388888</v>
+        <v>3.6111112</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>20810</v>
+        <v>20229</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D216" t="n">
-        <v>4.4166665</v>
+        <v>3.6111112</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>20811</v>
+        <v>20260</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D217" t="n">
-        <v>4.2222223</v>
+        <v>3.6111112</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>20812</v>
+        <v>20291</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="D218" t="n">
-        <v>4.5</v>
+        <v>3.6666667</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>20837</v>
+        <v>20304</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="D219" t="n">
-        <v>2.5277777</v>
+        <v>3.6666667</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>20838</v>
+        <v>20332</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D220" t="n">
-        <v>2.6111112</v>
+        <v>3.6666667</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>20839</v>
+        <v>20359</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D221" t="n">
-        <v>2.6944444</v>
+        <v>3.6944444</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>20840</v>
+        <v>20419</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D222" t="n">
-        <v>2.7777777</v>
+        <v>3.7222221</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>20841</v>
+        <v>20448</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D223" t="n">
-        <v>2.7222223</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>20842</v>
+        <v>20477</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D224" t="n">
-        <v>2.8888888</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>20843</v>
+        <v>20506</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D225" t="n">
-        <v>2.8888888</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>20862</v>
+        <v>20537</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D226" t="n">
-        <v>3.75</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>20863</v>
+        <v>20568</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D227" t="n">
-        <v>3.8611112</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>20864</v>
+        <v>20599</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C228" t="n">
         <v>2016</v>
       </c>
       <c r="D228" t="n">
-        <v>3.3611112</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>20865</v>
+        <v>20629</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>2017</v>
       </c>
       <c r="D229" t="n">
-        <v>3.4722223</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>20866</v>
+        <v>20660</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D230" t="n">
-        <v>3.5277777</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>20867</v>
+        <v>20715</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D231" t="n">
-        <v>3.5277777</v>
+        <v>3.7222223</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>20868</v>
+        <v>20744</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -4135,90 +4135,90 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D232" t="n">
-        <v>3.6111112</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>20892</v>
+        <v>20775</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D233" t="n">
-        <v>2.4166667</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>20893</v>
+        <v>20806</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D234" t="n">
-        <v>2.4722221</v>
+        <v>3.7777777</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>20894</v>
+        <v>20837</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D235" t="n">
-        <v>2.9722221</v>
+        <v>3.7777777</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>20895</v>
+        <v>20862</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D236" t="n">
-        <v>2.9722221</v>
+        <v>3.7777777</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>20896</v>
+        <v>20892</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D237" t="n">
-        <v>2.9166667</v>
+        <v>3.7777777</v>
       </c>
     </row>
     <row r="238">
@@ -4227,14 +4227,14 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D238" t="n">
-        <v>2.9166667</v>
+        <v>3.7777777</v>
       </c>
     </row>
     <row r="239">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D239" t="n">
-        <v>3.0277777</v>
+        <v>3.8055556</v>
       </c>
     </row>
     <row r="240">
@@ -4259,14 +4259,14 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C240" t="n">
         <v>2014</v>
       </c>
       <c r="D240" t="n">
-        <v>0.58333331</v>
+        <v>3.8333333</v>
       </c>
     </row>
     <row r="241">
@@ -4275,14 +4275,14 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D241" t="n">
-        <v>0.6388889</v>
+        <v>3.8333333</v>
       </c>
     </row>
     <row r="242">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D242" t="n">
-        <v>0.8888889</v>
+        <v>3.8333333</v>
       </c>
     </row>
     <row r="243">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D243" t="n">
-        <v>0.8888889</v>
+        <v>3.8333333</v>
       </c>
     </row>
     <row r="244">
@@ -4323,14 +4323,14 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D244" t="n">
-        <v>0.8888889</v>
+        <v>3.8333333</v>
       </c>
     </row>
     <row r="245">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D245" t="n">
-        <v>0.8888889</v>
+        <v>3.8611112</v>
       </c>
     </row>
     <row r="246">
@@ -4355,14 +4355,14 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D246" t="n">
-        <v>0.8888889</v>
+        <v>3.8611112</v>
       </c>
     </row>
     <row r="247">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C247" t="n">
         <v>2014</v>
       </c>
       <c r="D247" t="n">
-        <v>2.75</v>
+        <v>3.8888888</v>
       </c>
     </row>
     <row r="248">
@@ -4387,14 +4387,14 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C248" t="n">
         <v>2015</v>
       </c>
       <c r="D248" t="n">
-        <v>2.8888888</v>
+        <v>3.8888888</v>
       </c>
     </row>
     <row r="249">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D249" t="n">
-        <v>2.7777777</v>
+        <v>3.8888888</v>
       </c>
     </row>
     <row r="250">
@@ -4419,14 +4419,14 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C250" t="n">
         <v>2017</v>
       </c>
       <c r="D250" t="n">
-        <v>2.8333333</v>
+        <v>3.8888888</v>
       </c>
     </row>
     <row r="251">
@@ -4435,14 +4435,14 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D251" t="n">
-        <v>2.8611112</v>
+        <v>3.8888888</v>
       </c>
     </row>
     <row r="252">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D252" t="n">
-        <v>2.9444444</v>
+        <v>3.9166667</v>
       </c>
     </row>
     <row r="253">
@@ -4467,14 +4467,14 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D253" t="n">
-        <v>3.1388888</v>
+        <v>3.9166667</v>
       </c>
     </row>
     <row r="254">
@@ -4483,14 +4483,14 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D254" t="n">
-        <v>1.8611112</v>
+        <v>3.9444444</v>
       </c>
     </row>
     <row r="255">
@@ -4499,14 +4499,14 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D255" t="n">
-        <v>1.9722222</v>
+        <v>3.9444444</v>
       </c>
     </row>
     <row r="256">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C256" t="n">
         <v>2016</v>
       </c>
       <c r="D256" t="n">
-        <v>2.5277777</v>
+        <v>3.9444444</v>
       </c>
     </row>
     <row r="257">
@@ -4531,14 +4531,14 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D257" t="n">
-        <v>2.5277777</v>
+        <v>3.9444444</v>
       </c>
     </row>
     <row r="258">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D258" t="n">
-        <v>2.6944444</v>
+        <v>3.9444444</v>
       </c>
     </row>
     <row r="259">
@@ -4563,14 +4563,14 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D259" t="n">
-        <v>2.6944444</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260">
@@ -4579,14 +4579,14 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D260" t="n">
-        <v>2.8333333</v>
+        <v>4.0277777</v>
       </c>
     </row>
     <row r="261">
@@ -4595,14 +4595,14 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D261" t="n">
-        <v>0.75</v>
+        <v>4.0277777</v>
       </c>
     </row>
     <row r="262">
@@ -4611,14 +4611,14 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C262" t="n">
         <v>2015</v>
       </c>
       <c r="D262" t="n">
-        <v>0.75</v>
+        <v>4.0277777</v>
       </c>
     </row>
     <row r="263">
@@ -4627,14 +4627,14 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0833334</v>
+        <v>4.0277777</v>
       </c>
     </row>
     <row r="264">
@@ -4643,14 +4643,14 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D264" t="n">
-        <v>1.25</v>
+        <v>4.0555553</v>
       </c>
     </row>
     <row r="265">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D265" t="n">
-        <v>1.3055556</v>
+        <v>4.0555553</v>
       </c>
     </row>
     <row r="266">
@@ -4675,14 +4675,14 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D266" t="n">
-        <v>1.5555556</v>
+        <v>4.0555553</v>
       </c>
     </row>
     <row r="267">
@@ -4691,14 +4691,14 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D267" t="n">
-        <v>1.6388888</v>
+        <v>4.0555553</v>
       </c>
     </row>
     <row r="268">
@@ -4707,14 +4707,14 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C268" t="n">
         <v>2014</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0833334</v>
+        <v>4.1111112</v>
       </c>
     </row>
     <row r="269">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D269" t="n">
-        <v>1.0833334</v>
+        <v>4.1111112</v>
       </c>
     </row>
     <row r="270">
@@ -4739,14 +4739,14 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C270" t="n">
         <v>2016</v>
       </c>
       <c r="D270" t="n">
-        <v>1.1666666</v>
+        <v>4.1388888</v>
       </c>
     </row>
     <row r="271">
@@ -4755,14 +4755,14 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C271" t="n">
         <v>2017</v>
       </c>
       <c r="D271" t="n">
-        <v>1.1666666</v>
+        <v>4.1388888</v>
       </c>
     </row>
     <row r="272">
@@ -4771,14 +4771,14 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D272" t="n">
-        <v>1.1666666</v>
+        <v>4.1666665</v>
       </c>
     </row>
     <row r="273">
@@ -4787,14 +4787,14 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C273" t="n">
         <v>2019</v>
       </c>
       <c r="D273" t="n">
-        <v>1.1666666</v>
+        <v>4.1666665</v>
       </c>
     </row>
     <row r="274">
@@ -4803,14 +4803,14 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D274" t="n">
-        <v>1.1666666</v>
+        <v>4.2222223</v>
       </c>
     </row>
     <row r="275">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D275" t="n">
-        <v>0.8611111</v>
+        <v>4.2222223</v>
       </c>
     </row>
     <row r="276">
@@ -4835,14 +4835,14 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D276" t="n">
-        <v>0.8611111</v>
+        <v>4.2222223</v>
       </c>
     </row>
     <row r="277">
@@ -4851,14 +4851,14 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D277" t="n">
-        <v>0.8611111</v>
+        <v>4.4166665</v>
       </c>
     </row>
     <row r="278">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D278" t="n">
-        <v>0.8611111</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="279">
@@ -4883,14 +4883,14 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C279" t="n">
         <v>2018</v>
       </c>
       <c r="D279" t="n">
-        <v>0.91666669</v>
+        <v>4.5555553</v>
       </c>
     </row>
     <row r="280">
@@ -4899,14 +4899,14 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C280" t="n">
         <v>2019</v>
       </c>
       <c r="D280" t="n">
-        <v>0.8611111</v>
+        <v>4.7222223</v>
       </c>
     </row>
     <row r="281">
@@ -4915,14 +4915,14 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C281" t="n">
         <v>2020</v>
       </c>
       <c r="D281" t="n">
-        <v>0.91666669</v>
+        <v>4.8888888</v>
       </c>
     </row>
   </sheetData>
